--- a/WindModel/maxima.xlsx
+++ b/WindModel/maxima.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\MatLab\WindModel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{79D15B26-6BDE-4AE6-AE1B-2846857F5DD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACE74561-1475-4969-942A-C39BDFFDD128}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18600" yWindow="1170" windowWidth="28800" windowHeight="15240" xr2:uid="{3CE20909-E06E-48E8-A394-E5CA7D96EFAF}"/>
+    <workbookView xWindow="8910" yWindow="3495" windowWidth="28800" windowHeight="15240" xr2:uid="{3CE20909-E06E-48E8-A394-E5CA7D96EFAF}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="2" r:id="rId1"/>
@@ -424,7 +424,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{080F31F5-7D7C-4714-8BD1-E09F49C5FA6E}">
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="16384" width="9.140625" style="1"/>
@@ -536,81 +536,73 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B14" s="1">
-        <v>16.2</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="B15" s="1">
-        <v>14.9</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="B16" s="1">
-        <v>17.3</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="B17" s="1">
-        <v>15.5</v>
+        <v>17.399999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B18" s="1">
-        <v>17.399999999999999</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B19" s="1">
-        <v>17.8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B20" s="1">
-        <v>20</v>
+        <v>17.399999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B21" s="1">
-        <v>17.399999999999999</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B22" s="1">
-        <v>15.3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="1">
-        <v>2024</v>
-      </c>
-      <c r="B23" s="1">
         <v>14.3</v>
       </c>
     </row>
